--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_5.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_5.xlsx
@@ -26261,7 +26261,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="C2" t="n">
         <v>26876.8513828616</v>
@@ -26273,7 +26273,7 @@
         <v>26876.8513828616</v>
       </c>
       <c r="F2" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="G2" t="n">
         <v>26876.8513828616</v>
@@ -26285,10 +26285,10 @@
         <v>26876.8513828616</v>
       </c>
       <c r="J2" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="K2" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="L2" t="n">
         <v>26876.8513828616</v>
@@ -26297,7 +26297,7 @@
         <v>26876.8513828616</v>
       </c>
       <c r="N2" t="n">
-        <v>26876.8513828616</v>
+        <v>26876.85138286161</v>
       </c>
       <c r="O2" t="n">
         <v>26876.8513828616</v>
@@ -26469,7 +26469,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6750.74861713839</v>
+        <v>-6750.748617138397</v>
       </c>
       <c r="C6" t="n">
         <v>-6750.748617138397</v>
@@ -26481,7 +26481,7 @@
         <v>26876.8513828616</v>
       </c>
       <c r="F6" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="G6" t="n">
         <v>26876.8513828616</v>
@@ -26493,10 +26493,10 @@
         <v>26876.8513828616</v>
       </c>
       <c r="J6" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="K6" t="n">
-        <v>26876.85138286161</v>
+        <v>26876.8513828616</v>
       </c>
       <c r="L6" t="n">
         <v>26876.8513828616</v>
@@ -26505,7 +26505,7 @@
         <v>26876.8513828616</v>
       </c>
       <c r="N6" t="n">
-        <v>26876.8513828616</v>
+        <v>26876.85138286161</v>
       </c>
       <c r="O6" t="n">
         <v>26876.8513828616</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
